--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -110,13 +110,13 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>GameMapTable</t>
-  </si>
-  <si>
-    <t>GameMapConfig</t>
-  </si>
-  <si>
-    <t>GameMapTable@game_map.xlsx</t>
+    <t>CardTable</t>
+  </si>
+  <si>
+    <t>CardConfig</t>
+  </si>
+  <si>
+    <t>CardTable@card.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1201,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" display="GameMapTable@game_map.xlsx" tooltip="mailto:GameMapTable@game_map.xlsx"/>
+    <hyperlink ref="E4" r:id="rId1" display="CardTable@card.xlsx" tooltip="mailto:CardTable@card.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -117,6 +117,15 @@
   </si>
   <si>
     <t>CardTable@card.xlsx</t>
+  </si>
+  <si>
+    <t>GhostTable</t>
+  </si>
+  <si>
+    <t>GhostConfig</t>
+  </si>
+  <si>
+    <t>GhostTable@ghost.xlsx</t>
   </si>
 </sst>
 </file>
@@ -732,7 +741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,9 +749,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1178,8 +1184,19 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="5:5">
-      <c r="E5" s="3"/>
+    <row r="5" spans="2:5">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="5:5">
       <c r="E6" s="2"/>
@@ -1202,6 +1219,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="CardTable@card.xlsx" tooltip="mailto:CardTable@card.xlsx"/>
+    <hyperlink ref="E5" r:id="rId2" display="GhostTable@ghost.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>GhostTable@ghost.xlsx</t>
+  </si>
+  <si>
+    <t>MaskTable</t>
+  </si>
+  <si>
+    <t>MaskConfig</t>
+  </si>
+  <si>
+    <t>MaskTable@mask.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1198,8 +1207,19 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="5:5">
-      <c r="E6" s="2"/>
+    <row r="6" spans="2:5">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="5:5">
       <c r="E7" s="2"/>
@@ -1220,6 +1240,7 @@
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="CardTable@card.xlsx" tooltip="mailto:CardTable@card.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="GhostTable@ghost.xlsx"/>
+    <hyperlink ref="E6" r:id="rId3" display="MaskTable@mask.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>MaskTable@mask.xlsx</t>
+  </si>
+  <si>
+    <t>SpecialTable</t>
+  </si>
+  <si>
+    <t>SpecialConfig</t>
+  </si>
+  <si>
+    <t>SpecialTable@special.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1080,12 +1089,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="43.5982142857143" customWidth="1"/>
+    <col min="5" max="5" width="43.6" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1179,7 +1188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="1:11">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -1193,7 +1202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:11">
       <c r="B5" t="s">
         <v>30</v>
       </c>
@@ -1207,7 +1216,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:11">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -1221,19 +1230,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="5:5">
-      <c r="E7" s="2"/>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="8" spans="5:5">
+    <row r="8" spans="1:11">
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="5:5">
+    <row r="9" spans="1:11">
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="5:5">
+    <row r="10" spans="1:11">
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="5:5">
+    <row r="11" spans="1:11">
       <c r="E11" s="2"/>
     </row>
   </sheetData>
@@ -1241,6 +1261,7 @@
     <hyperlink ref="E4" r:id="rId1" display="CardTable@card.xlsx" tooltip="mailto:CardTable@card.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="GhostTable@ghost.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="MaskTable@mask.xlsx"/>
+    <hyperlink ref="E7" r:id="rId4" display="SpecialTable@special.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="29100" windowHeight="12700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -135,15 +135,6 @@
   </si>
   <si>
     <t>MaskTable@mask.xlsx</t>
-  </si>
-  <si>
-    <t>SpecialTable</t>
-  </si>
-  <si>
-    <t>SpecialConfig</t>
-  </si>
-  <si>
-    <t>SpecialTable@special.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1089,12 +1080,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="43.6" customWidth="1"/>
+    <col min="5" max="5" width="43.5982142857143" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1188,7 +1179,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="2:5">
       <c r="B4" t="s">
         <v>27</v>
       </c>
@@ -1202,7 +1193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>30</v>
       </c>
@@ -1216,7 +1207,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
         <v>33</v>
       </c>
@@ -1230,30 +1221,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>38</v>
-      </c>
+    <row r="7" spans="5:5">
+      <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="5:5">
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="5:5">
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="5:5">
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="5:5">
       <c r="E11" s="2"/>
     </row>
   </sheetData>
@@ -1261,7 +1241,6 @@
     <hyperlink ref="E4" r:id="rId1" display="CardTable@card.xlsx" tooltip="mailto:CardTable@card.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="GhostTable@ghost.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="MaskTable@mask.xlsx"/>
-    <hyperlink ref="E7" r:id="rId4" display="SpecialTable@special.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>MaskTable@mask.xlsx</t>
+  </si>
+  <si>
+    <t>MengpoTable</t>
+  </si>
+  <si>
+    <t>MengpoConfig</t>
+  </si>
+  <si>
+    <t>MengpoTable@special.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1221,8 +1230,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="5:5">
-      <c r="E7" s="2"/>
+    <row r="7" spans="2:5">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="5:5">
       <c r="E8" s="2"/>
@@ -1241,6 +1261,7 @@
     <hyperlink ref="E4" r:id="rId1" display="CardTable@card.xlsx" tooltip="mailto:CardTable@card.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="GhostTable@ghost.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="MaskTable@mask.xlsx"/>
+    <hyperlink ref="E7" r:id="rId4" display="MengpoTable@special.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Configs/source/Datas/__tables__.xlsx
+++ b/Configs/source/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -144,6 +144,15 @@
   </si>
   <si>
     <t>MengpoTable@special.xlsx</t>
+  </si>
+  <si>
+    <t>BuffTable</t>
+  </si>
+  <si>
+    <t>BuffConfig</t>
+  </si>
+  <si>
+    <t>BuffTable@buff.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1244,8 +1253,19 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="5:5">
-      <c r="E8" s="2"/>
+    <row r="8" spans="2:5">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="5:5">
       <c r="E9" s="2"/>
@@ -1262,6 +1282,7 @@
     <hyperlink ref="E5" r:id="rId2" display="GhostTable@ghost.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="MaskTable@mask.xlsx"/>
     <hyperlink ref="E7" r:id="rId4" display="MengpoTable@special.xlsx"/>
+    <hyperlink ref="E8" r:id="rId5" display="BuffTable@buff.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
